--- a/output/2026-09-20_13_Croazia_Splitsko-dalmatinska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-20_13_Croazia_Splitsko-dalmatinska_Componentistica_Ventilazione_industriale.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,6 @@
           <t>Commercio all'ingrosso, installazione e assistenza impianti climatizzazione/ventilazione; vendita climatizzatori, unita GHP e apparecchiature di ventilazione</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Esistenza confermata (fininfo, kompass, moja-djelatnost). Attiva dal 1995, modello di vendita all'ingrosso compatibile con profilo distributore. Rappresentanza marchi Toshiba/Mitsubishi/Stulz/Aisin Toyota non confermata da fonti pubbliche; telefono ed email non verificabili, lasciati vuoti.</t>
@@ -606,7 +605,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
